--- a/input/PL/reg_retirement.xlsx
+++ b/input/PL/reg_retirement.xlsx
@@ -16,137 +16,158 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="129" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="150" uniqueCount="59">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Last edit:</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Process:</t>
+  </si>
+  <si>
+    <t>R1a</t>
+  </si>
+  <si>
+    <t>R1b</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Modelparametersgoverningproje</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
   <si>
     <t>Description:</t>
   </si>
   <si>
-    <t>Model parameters governing projection of retirement</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>Last edit:</t>
-  </si>
-  <si>
-    <t>12 Jan 2016 AB</t>
-  </si>
-  <si>
-    <t>Process:</t>
-  </si>
-  <si>
-    <t>R1a</t>
-  </si>
-  <si>
     <t>Probit regression estimates of the probability of retiring, single individuals aged 50+ not yet retired</t>
   </si>
   <si>
-    <t>R1b</t>
-  </si>
-  <si>
     <t>Probit regression estimates of the probability of retiring, partnered individuals aged 50+ not yet retired</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t>R1a - Retirement single</t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>R1b - Retirement partnered</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>Dgn</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag_sq</t>
+  </si>
+  <si>
+    <t>Elig_pen</t>
+  </si>
+  <si>
+    <t>Elig_pen_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Medium_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low_L1</t>
+  </si>
+  <si>
+    <t>Reached_Retirement_Age</t>
+  </si>
+  <si>
+    <t>Les_c3_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q2_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q3_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q4_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q5_L1</t>
+  </si>
+  <si>
+    <t>Dlltsd_L1</t>
+  </si>
+  <si>
+    <t>PL4</t>
+  </si>
+  <si>
+    <t>PL5</t>
+  </si>
+  <si>
+    <t>PL6</t>
+  </si>
+  <si>
+    <t>PL10</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Post2015</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
     <t>COEFFICIENT</t>
   </si>
   <si>
-    <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag_sq</t>
-  </si>
-  <si>
-    <t>Elig_pen</t>
-  </si>
-  <si>
-    <t>Elig_pen_L1</t>
-  </si>
-  <si>
-    <t>Deh_c4_Medium_L1</t>
-  </si>
-  <si>
-    <t>Deh_c4_Low_L1</t>
-  </si>
-  <si>
-    <t>Reached_Retirement_Age</t>
-  </si>
-  <si>
-    <t>Les_c3_NotEmployed_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q2_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q3_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q4_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q5_L1</t>
-  </si>
-  <si>
-    <t>Dlltsd_L1</t>
-  </si>
-  <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>PL10</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Post2015</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>R1a - Retirement single</t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
-  </si>
-  <si>
     <t>Reached_Retirement_Age_Les_c3_NotEmployed_L1</t>
   </si>
   <si>
@@ -171,98 +192,17 @@
     <t>Y2023</t>
   </si>
   <si>
-    <t>R1b - Retirement partnered</t>
+    <t>Reached_Retirement_Age_Les_c3_No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="19">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -273,7 +213,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -281,111 +221,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,59 +242,83 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
+      <c r="A10" t="s">
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -464,73 +331,170 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.27699452385827339</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1">
         <v>1103.493090171497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
         <v>13978</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1">
         <v>-2886006.5795061616</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.31961966841684009</v>
       </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11">
+        <v>24</v>
+      </c>
+      <c r="F11" s="1">
         <v>3269.1818930134959</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
         <v>44875</v>
       </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
       <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1">
         <v>-7243305.1759752929</v>
       </c>
     </row>
@@ -540,1571 +504,1568 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="N1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="U1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="V1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="W1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.049592535931356464</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0044283755227153849</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-0.0014430097985730708</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>9.7829959375248692e-06</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-0.0021172434345822608</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-0.0016258765681565176</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-2.1388794535409476e-05</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-8.7941749664378552e-05</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.0045817341566803029</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0.00043424395381411358</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>0.00012956445544328333</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>0.00011589155012927885</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>3.6496390283855158e-05</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>4.7571160241934897e-05</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-0.00046375678788256307</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-6.0999451601891248e-05</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>0.00039786380380332602</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>0.00010572375063801556</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-0.00014604531830605429</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-8.5334412318319956e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>0.00055309577719119679</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>0.048745591062778537</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1">
         <v>0.0073291151871324751</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-0.0014430097985730708</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.0065134921580479177</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-5.0319183983452229e-05</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-0.00040207468703208626</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-0.00077341602360153812</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-7.3292798788666264e-05</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.00060416482202877569</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-0.0032729222621302317</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-0.00050771599127464803</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-0.00066857862539507901</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-0.00046764602210130901</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-0.00019648529751053329</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-0.00047853095985542909</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-0.00047133543544564116</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>0.00034770472546199332</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-2.1609999854760309e-05</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-0.00021199195705957213</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>0.00018512704791803086</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>-4.2627686941451581e-05</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-6.364509967000942e-05</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>-0.2044701489541163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.00055348166092928307</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>9.7829959375248692e-06</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-5.0319183983452229e-05</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>3.9216593179906336e-07</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>6.542099476591765e-06</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>9.1004940022310905e-06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>6.1277649556390652e-07</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-4.935786234882666e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.9529974796699857e-05</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>3.6650280709337336e-06</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>5.1646668312623476e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>3.6717877848814495e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>2.0643162590269141e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>3.7145540467382692e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>3.6338385213912218e-06</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-2.5858388531499097e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-1.5343659756834362e-07</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>1.5447207582832139e-06</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>-1.3230383907558664e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>3.2093635652056943e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>5.3198958825000694e-07</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>0.0015693677353458765</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.7372681897098059</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-0.0021172434345822608</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-0.00040207468703208626</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>6.542099476591765e-06</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.0091089938441783411</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.004971374344784763</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-0.00019338766783658426</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-0.00016186512937145926</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-0.0077700917308647661</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0.00023405637918176862</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-0.00011897533193336567</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-0.00025800140730049292</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-6.446476769526757e-05</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-0.00070424604027825594</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-0.00066861873806182482</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-9.8807187009851199e-05</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-0.000585577023048986</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>-6.3186669907354213e-05</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-0.00015143640669083207</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-3.6992006411441e-05</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>0.00014254334553627339</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>0.0040000877827012782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.85739770140274341</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-0.0016258765681565176</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-0.00077341602360153812</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>9.1004940022310905e-06</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.004971374344784763</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.009681124784836407</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>-0.00022170890383852847</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-0.0002100979178697982</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-0.0068831121909954957</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>6.8430977453601749e-05</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.9115436813251473e-05</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-0.00025224579934706413</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-0.00016182662112764444</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-0.00087589208272496324</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-0.00064442841006506334</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-1.1299343583856883e-05</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-0.00032908605291263751</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-2.9176351311750205e-05</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-0.00012612794344929587</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>-4.8805724514656458e-06</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>6.7536303240462239e-05</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>0.016061024965626169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.042592477086305862</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-2.1388794535409476e-05</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-7.3292798788666264e-05</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>6.1277649556390652e-07</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-0.00019338766783658426</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>-0.00022170890383852847</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0071299122401152068</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.0067363742695617321</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.00063397209758850727</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-0.0006048912457429918</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>0.00013241502224967165</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>0.00019771540596689172</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>0.00043762554285607376</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>0.0031986964691964239</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>0.00016201741586127478</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>0.00011735875031317864</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>3.9694238468183842e-05</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-5.4570599838733034e-05</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-0.00010512145767239809</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>9.2598024204704454e-05</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>-0.00051644568135107737</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-0.0058101557832410805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.17850449606521537</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-8.7941749664378552e-05</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.00060416482202877569</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-4.935786234882666e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-0.00016186512937145926</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-0.0002100979178697982</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.0067363742695617321</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.010056654854702965</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.00031664852929041021</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-0.00086675724174440933</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>8.357939184817139e-05</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>0.00054592384315993144</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>0.001198875129389391</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>0.0042583944249218126</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>0.00022983290397530923</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-7.6466814873776823e-05</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-0.00026981671105235456</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-0.00062901816812909774</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-0.0006584498789577863</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.00012337578026696752</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-0.00045077966456271573</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>-0.027017386378032554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.50133391779502356</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.0045817341566803029</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-0.0032729222621302317</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>1.9529974796699857e-05</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-0.0077700917308647661</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-0.0068831121909954957</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>0.00063397209758850727</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.00031664852929041021</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.015877436186470514</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-0.00028657955724399999</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0006009793994534024</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.0012537387834633471</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>3.4398899499129415e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>0.0010686875057935342</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>0.0014421879738432918</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-0.00048308124828565571</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>0.00094058240665704194</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>0.00027828450313734099</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>4.4486850863643262e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-8.8199892545541558e-05</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>0.00079649322211328838</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>0.11770444455896656</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1">
         <v>-0.1216868903534202</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.00043424395381411358</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-0.00050771599127464803</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>3.6650280709337336e-06</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.00023405637918176862</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>6.8430977453601749e-05</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-0.0006048912457429918</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-0.00086675724174440933</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-0.00028657955724399999</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.011096248713752017</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-0.00022358244484684724</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0059106816449758705</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.00963965932486807</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>0.009434178450034858</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-0.0017427664033057427</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>4.5012099544818659e-05</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-0.00031170102987654628</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-0.0007100956486376141</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>0.00039987710643275181</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>7.1083555897450247e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>0.00014516330979342813</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.0066014818758532434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.011647953872456884</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.00012956445544328333</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-0.00066857862539507901</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>5.1646668312623476e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-0.00011897533193336567</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.9115436813251473e-05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>0.00013241502224967165</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>8.357939184817139e-05</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0006009793994534024</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-0.00022358244484684724</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0043995097623575306</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0025294457650854038</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.0025802584688963811</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>0.0026033196085098677</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>0.00065914795727179992</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>0.0001680932262500337</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>6.0737678159236718e-05</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>0.00018657286629224386</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-0.00020956912094455987</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-4.0186154442651347e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>9.9573447714218716e-05</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>0.019086917374537452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.10028965916987145</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>0.00011589155012927885</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-0.00046764602210130901</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>3.6717877848814495e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-0.00025800140730049292</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-0.00025224579934706413</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>0.00019771540596689172</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>0.00054592384315993144</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>0.0012537387834633471</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0059106816449758705</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0025294457650854038</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0091453368192735782</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.009224976732038398</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>0.0091725576747186</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>0.00078649646081538501</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-0.00019192664012827399</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-0.00034239739399968003</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-0.00048298522555910309</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-0.00035332174057129675</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-4.8703482893935977e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>4.1668420069442685e-05</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.0059550254970396899</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1">
         <v>-0.099274474182055733</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>3.6496390283855158e-05</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-0.00019648529751053329</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>2.0643162590269141e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-6.446476769526757e-05</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-0.00016182662112764444</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>0.00043762554285607376</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>0.001198875129389391</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>3.4398899499129415e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.00963965932486807</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.0025802584688963811</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.009224976732038398</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.016912073884976501</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.013338702113984614</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.00089422910401553823</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-0.00016468486888053524</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-0.0010426971129527478</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-0.0010231153508205157</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-0.00058879333414215513</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-5.0137126425449222e-05</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-8.4299124617445188e-05</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-0.0077694834541015001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1">
         <v>-0.2492186769925612</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>4.7571160241934897e-05</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-0.00047853095985542909</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>3.7145540467382692e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-0.00070424604027825594</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-0.00087589208272496324</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>0.0031986964691964239</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>0.0042583944249218126</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>0.0010686875057935342</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0.009434178450034858</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>0.0026033196085098677</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>0.0091725576747186</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.013338702113984614</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.019469052464251912</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.00092244700524723609</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>-0.00053387776566981649</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-0.00089382837719058795</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-0.0012725177715787886</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>-0.00047665610049609517</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-6.4223941121098775e-06</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-3.1487299562720297e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>-0.00038907724292924772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.078523298093640032</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-0.00046375678788256307</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-0.00047133543544564116</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>3.6338385213912218e-06</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-0.00066861873806182482</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-0.00064442841006506334</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.00016201741586127478</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>0.00022983290397530923</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0.0014421879738432918</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-0.0017427664033057427</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>0.00065914795727179992</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>0.00078649646081538501</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.00089422910401553823</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.00092244700524723609</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0048964961258321244</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>-0.00012284760910439467</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-6.5415496667959021e-05</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-0.0001598066236644189</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-0.00042915604917894454</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-3.0509345372570131e-05</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>-0.00028118434110293092</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>0.014723921140990165</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.026712079146674641</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-6.0999451601891248e-05</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>0.00034770472546199332</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-2.5858388531499097e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-9.8807187009851199e-05</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-1.1299343583856883e-05</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>0.00011735875031317864</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-7.6466814873776823e-05</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-0.00048308124828565571</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>4.5012099544818659e-05</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>0.0001680932262500337</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-0.00019192664012827399</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-0.00016468486888053524</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-0.00053387776566981649</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>-0.00012284760910439467</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0065175833645131111</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.0031143438186941211</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.0031612501589851965</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.0031594580107916622</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>6.7565929643310636e-05</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-0.00062137019404185203</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-0.015075533503446661</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.07017203103490717</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>0.00039786380380332602</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-2.1609999854760309e-05</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-1.5343659756834362e-07</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-0.000585577023048986</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-0.00032908605291263751</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>3.9694238468183842e-05</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-0.00026981671105235456</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>0.00094058240665704194</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-0.00031170102987654628</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>6.0737678159236718e-05</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-0.00034239739399968003</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-0.0010426971129527478</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-0.00089382837719058795</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-6.5415496667959021e-05</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.0031143438186941211</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0081615946594039753</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.0031582283464525762</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>0.0031741276975958185</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>1.2112050360754407e-05</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-0.0004798446480533021</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-0.0011253340040447701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.053873164306078865</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>0.00010572375063801556</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-0.00021199195705957213</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>1.5447207582832139e-06</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>-6.3186669907354213e-05</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-2.9176351311750205e-05</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-5.4570599838733034e-05</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-0.00062901816812909774</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>0.00027828450313734099</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-0.0007100956486376141</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>0.00018657286629224386</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-0.00048298522555910309</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-0.0010231153508205157</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-0.0012725177715787886</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-0.0001598066236644189</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.0031612501589851965</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.0031582283464525762</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.006361724508715306</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.0031832471385811354</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>2.0968860297657158e-05</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-0.00031761003197093758</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>0.0046547884483261418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.11186177965333824</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-0.00014604531830605429</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>0.00018512704791803086</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>-1.3230383907558664e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>-0.00015143640669083207</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-0.00012612794344929587</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-0.00010512145767239809</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-0.0006584498789577863</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>4.4486850863643262e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0.00039987710643275181</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-0.00020956912094455987</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-0.00035332174057129675</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-0.00058879333414215513</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>-0.00047665610049609517</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-0.00042915604917894454</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.0031594580107916622</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>0.0031741276975958185</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.0031832471385811354</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.004767598788439761</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-7.5789463992425579e-07</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-0.00018445267361828581</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.0090577804955661867</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.031417234368560108</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-8.5334412318319956e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-4.2627686941451581e-05</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>3.2093635652056943e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-3.6992006411441e-05</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>-4.8805724514656458e-06</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>9.2598024204704454e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.00012337578026696752</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-8.8199892545541558e-05</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>7.1083555897450247e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-4.0186154442651347e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-4.8703482893935977e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-5.0137126425449222e-05</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-6.4223941121098775e-06</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-3.0509345372570131e-05</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>6.7565929643310636e-05</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>1.2112050360754407e-05</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>2.0968860297657158e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-7.5789463992425579e-07</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.00012681537220546969</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.00077803555044017201</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-0.00031334950363361147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21">
+        <v>47</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.50404850449953509</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>0.00055309577719119679</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-6.364509967000942e-05</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>5.3198958825000694e-07</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.00014254334553627339</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>6.7536303240462239e-05</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>-0.00051644568135107737</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-0.00045077966456271573</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>0.00079649322211328838</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0.00014516330979342813</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>9.9573447714218716e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>4.1668420069442685e-05</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-8.4299124617445188e-05</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-3.1487299562720297e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>-0.00028118434110293092</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-0.00062137019404185203</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-0.0004798446480533021</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-0.00031761003197093758</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-0.00018445267361828581</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.00077803555044017201</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.007472164387475241</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>0.010372610637007007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1">
         <v>-4.1473500162319086</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>0.048745591062778537</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-0.2044701489541163</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>0.0015693677353458765</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.0040000877827012782</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>0.016061024965626169</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-0.0058101557832410805</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>-0.027017386378032554</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>0.11770444455896656</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.0066014818758532434</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>0.019086917374537452</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.0059550254970396899</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>-0.0077694834541015001</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>-0.00038907724292924772</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>0.014723921140990165</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-0.015075533503446661</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-0.0011253340040447701</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>0.0046547884483261418</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.0090577804955661867</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-0.00031334950363361147</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>0.010372610637007007</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>6.496367362402637</v>
       </c>
     </row>
@@ -2113,2678 +2074,2675 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac">
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" t="s">
         <v>43</v>
       </c>
-      <c r="M1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>44</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>45</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>46</v>
       </c>
-      <c r="U1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="AB1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD1" t="s">
         <v>48</v>
-      </c>
-      <c r="W1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.15678759747782323</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0017575568202877149</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-0.00037271417944368941</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1.8719379187581219e-06</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-0.00090231017838995637</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-0.00069757470688825872</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>4.4425539359404208e-06</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>6.4976060688815528e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.002078414164731725</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0.00088782390245072487</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-0.00031037546210686763</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-5.2121450658629796e-05</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>0.00011385149150103724</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>2.882400653353716e-05</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-7.1180977395114204e-05</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-0.00069320876602668659</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-5.4814436400148041e-05</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>0.00015128457546006134</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>8.0128530894044928e-05</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-6.9090894662101297e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>6.9571328676916672e-05</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-0.00025444586197862027</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="1">
         <v>-7.3894526271214671e-05</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>-0.00024302535574699004</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>-0.00019984048134990217</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>2.1444089854963171e-05</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>-0.00014009768424022573</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>-4.6906386195071786e-05</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>0.013701474688218678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1">
         <v>0.27158873304770442</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-0.00037271417944368941</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.0046748786715602834</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-3.8255582520552349e-05</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-0.0013489198748415712</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-0.0013534757009172442</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>9.4106095732826339e-05</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.00025725002094433014</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>3.0456363122755709e-05</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-0.0012635435095719322</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>0.00098976597648192492</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>4.2809717230583508e-05</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-0.0004111478684739947</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-0.00042108554014620887</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-0.00040432064004843494</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>0.00019055061330546658</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>0.000672517382368093</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-0.0010598067095275304</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-0.00090260039600047193</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>-0.00011639641353401904</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-8.6944669574224448e-05</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>0.00030905641687004048</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>0.00010353183581316219</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>0.00025893234521229963</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>0.00030593314854043298</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>-3.4503734812061423e-05</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>0.0002356216591192159</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>0.00080552715129966757</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>-0.14058478513640041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.0018524847500672387</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1.8719379187581219e-06</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-3.8255582520552349e-05</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>3.1598293522283368e-07</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>1.2632862169006975e-05</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>1.2413219119321799e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-7.5582221757300259e-07</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-2.1681530814087521e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-3.3451953054003814e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>9.5704419277477853e-06</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-7.7947728559349302e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-2.2511041450069521e-07</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>3.0382632259664893e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>3.3829331408300573e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>3.2749282788656398e-06</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-1.2582308060409941e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-6.8147082045526795e-06</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>9.3003271143169254e-06</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>7.8848899661843465e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>8.4808967769467556e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>7.820747626408281e-07</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-2.2023311793803913e-06</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="1">
         <v>-7.0474589703456588e-07</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="1">
         <v>-1.7915606807792132e-06</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="1">
         <v>-2.3790766378102053e-06</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="1">
         <v>2.541625622577576e-07</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="1">
         <v>-1.7413920244386096e-06</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="1">
         <v>-6.8117122805056406e-06</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="1">
         <v>0.0011422518568260955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.28657748958991486</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-0.00090231017838995637</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-0.0013489198748415712</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>1.2632862169006975e-05</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.0043734188179216406</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.0028528118693712749</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-0.00027972492526581619</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>4.4967977335159774e-05</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-0.0038554817266619346</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-0.00034764311807667248</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-8.6301713204031856e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>9.6022106257032981e-05</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-0.0001901569731814802</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-9.7602915247296156e-05</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-0.00010333604334471485</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>0.00013005612827941045</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-5.4757104067465479e-05</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>9.6426344313751272e-05</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>1.8043561853149648e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-0.0001023942288142757</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>1.970331722432779e-05</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>7.5743542655586776e-05</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="1">
         <v>0.00010180699470342669</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="1">
         <v>0.00011350113251927876</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="1">
         <v>-1.2857853343623861e-05</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="1">
         <v>-2.9307412868472926e-05</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="1">
         <v>0.00014213532810521817</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="1">
         <v>-0.00027005352753556658</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="1">
         <v>0.037121382055087887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.71287649039357903</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-0.00069757470688825872</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-0.0013534757009172442</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>1.2413219119321799e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.0028528118693712749</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0050634864287170903</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>-0.00021923358679691899</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-4.5736558806905477e-05</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-0.0035091645146556882</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-0.00024345411732390595</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>0.00011738285427593132</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>0.00028489401400076751</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-0.00010944200814303785</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-6.4036910067599142e-05</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-6.1566052407227524e-05</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>9.940941965757167e-05</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-0.00021078691488813847</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>0.00019748895890510723</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>9.9950698639376945e-05</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>-3.499973999983438e-05</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>-5.9812013799018585e-06</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>4.5740422671740333e-05</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="1">
         <v>6.3612953440067132e-05</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="1">
         <v>4.1788134053605958e-05</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="1">
         <v>7.9016643521681584e-07</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="1">
         <v>-2.8643883068854331e-05</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="1">
         <v>0.00012307294235631983</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="1">
         <v>-0.00012268297274519238</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="1">
         <v>0.037841740808914712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.044177871289619947</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>4.4425539359404208e-06</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>9.4106095732826339e-05</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-7.5582221757300259e-07</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-0.00027972492526581619</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>-0.00021923358679691899</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0024827750111800161</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.0022299555918112121</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.0005927525079096103</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>5.8916593322035034e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-0.00039845403587474297</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>-3.3983075392934168e-05</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>8.5636241007488155e-05</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>0.00026256301163564519</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>0.00074696228118203392</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-1.2647275010513822e-05</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>0.00015298428650457993</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-9.7403745859787183e-05</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-0.00010779461062386766</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>0.00015077354205447096</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>2.9815800308848663e-05</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>5.8429132797410742e-05</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="1">
         <v>6.6867564640003802e-05</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="1">
         <v>0.00015588721984764682</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="1">
         <v>0.00022144781212160854</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="1">
         <v>5.9886420011594581e-06</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="1">
         <v>-5.7068512235385581e-05</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="1">
         <v>0.00036774185934003049</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="1">
         <v>-0.0058017586293908673</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.096694213241722782</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>6.4976060688815528e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.00025725002094433014</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-2.1681530814087521e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>4.4967977335159774e-05</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-4.5736558806905477e-05</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.0022299555918112121</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.0040729538496763664</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.00044202685452619849</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>3.7459856456783499e-05</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-0.00067200193374008046</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>-0.00013519655141374699</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>0.00010938864327033932</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>0.00047485207338392605</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>0.0010506496790185396</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>0.00013654720543211868</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>0.00010931447430294491</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-6.2267503210837764e-05</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-1.0165985295352165e-05</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.00018014772474622557</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-4.4823300580725174e-05</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>-5.3651335281894525e-05</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="1">
         <v>3.3329172839398764e-05</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="1">
         <v>8.004185158598672e-05</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="1">
         <v>2.498469268009414e-05</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="1">
         <v>3.2446506801741558e-05</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="1">
         <v>-0.00010551115575253259</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="1">
         <v>3.7360027614460369e-05</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="1">
         <v>-0.010963673573541305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1">
         <v>1.0301241387140763</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.002078414164731725</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>3.0456363122755709e-05</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-3.3451953054003814e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-0.0038554817266619346</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-0.0035091645146556882</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>0.0005927525079096103</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.00044202685452619849</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0074999123527830025</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0019073362327671696</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>-0.0023617523473726388</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-0.0002216703910971605</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>-4.3284102704975805e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>3.0004915487036148e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-6.7235913653528392e-05</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-0.00052339291551085042</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-0.00021549953571360463</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>0.00039465491332137635</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>0.00028729546376932494</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.00011597883398200204</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>0.00013233498735392216</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>-0.00034641005898824323</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="1">
         <v>-0.00017064293500240703</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="1">
         <v>-0.00034724802772401718</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="1">
         <v>-0.00033982728298824006</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="1">
         <v>6.119493947922747e-05</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="1">
         <v>-0.00051433985085248823</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="1">
         <v>-0.00064752532915221539</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
         <v>0.0058628253836812191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.26304653167458619</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.00088782390245072487</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-0.0012635435095719322</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>9.5704419277477853e-06</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-0.00034764311807667248</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-0.00024345411732390595</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>5.8916593322035034e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>3.7459856456783499e-05</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0019073362327671696</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0040099755310884777</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-0.0018437130631968304</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>-1.5399168746420841e-05</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.0016098950920857087</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>0.0023286386745741123</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>0.0027463966344201075</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-0.0013038711519999823</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-0.0001410696180749074</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>0.00026916697326754093</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>0.00029600308598087387</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>0.00063937756240875867</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>0.00032307995007107876</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>-0.0001884050393060146</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="1">
         <v>-0.00023078656662817821</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="1">
         <v>-0.00024042802444643576</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="1">
         <v>-0.00019277017087081932</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="1">
         <v>3.9449496683617311e-05</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="1">
         <v>-9.0537290877182059e-05</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="1">
         <v>-0.0006786283533652673</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
         <v>0.036400396432046414</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.050330628139069543</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-0.00031037546210686763</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.00098976597648192492</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-7.7947728559349302e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-8.6301713204031856e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>0.00011738285427593132</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-0.00039845403587474297</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-0.00067200193374008046</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>-0.0023617523473726388</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-0.0018437130631968304</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.004482847179347469</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.00013828735157754861</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.00077824446621538074</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>0.00056217094916910298</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>0.00059230996288851421</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>3.8074779593106787e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>0.00013691648243421492</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-0.00025091683418665086</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-0.00010302291932961128</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>0.00038562180615386198</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-0.0003406080050491531</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>0.00015993140580180653</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="1">
         <v>5.4313875407104289e-06</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="1">
         <v>0.00010196590264069556</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="1">
         <v>0.0002783875625854608</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="1">
         <v>-2.7431189977497359e-05</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="1">
         <v>0.00021031350628897142</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="1">
         <v>0.00076822779751108171</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="1">
         <v>-0.030164458624131398</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.033117951263190913</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-5.2121450658629796e-05</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>4.2809717230583508e-05</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-2.2511041450069521e-07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>9.6022106257032981e-05</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>0.00028489401400076751</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>-3.3983075392934168e-05</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-0.00013519655141374699</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-0.0002216703910971605</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>-1.5399168746420841e-05</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.00013828735157754861</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0038679004327374505</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.0018780801152901276</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>0.0018833430366302164</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>0.0018907475316374905</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>3.547966556504236e-05</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-4.6773360594432847e-05</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>8.7986299791329315e-05</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>4.1368283494710089e-06</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>2.4985499950073086e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-0.00014165866100096302</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>3.8742391354317039e-05</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="1">
         <v>-0.00010385866329858044</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="1">
         <v>0.0001083999031252918</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="1">
         <v>4.0935960010347774e-05</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="1">
         <v>-4.8204641563105729e-06</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="1">
         <v>-6.3517107127158186e-06</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="1">
         <v>0.00018316105101792235</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="1">
         <v>-0.003490167919082768</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.1631967223785934</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>0.00011385149150103724</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-0.0004111478684739947</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>3.0382632259664893e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-0.0001901569731814802</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-0.00010944200814303785</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>8.5636241007488155e-05</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>0.00010938864327033932</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>-4.3284102704975805e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.0016098950920857087</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.00077824446621538074</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.0018780801152901276</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0044505942236604708</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0041355496114984991</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.0046667826728765092</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-0.00021299043238716788</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>0.00018959289887824</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-0.00012839296382699409</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-3.869527838100211e-05</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>0.001298617951075188</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-0.0002420732303093111</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-7.9854444786652684e-05</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="1">
         <v>-0.00039287227748727101</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="1">
         <v>-0.00010359611343775492</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="1">
         <v>8.03628109896738e-05</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="1">
         <v>1.2494332885968593e-05</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="1">
         <v>-9.6553359474627672e-05</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="1">
         <v>0.00015215645559420133</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="1">
         <v>0.0083695773642136553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.0035469766583652636</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>2.882400653353716e-05</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-0.00042108554014620887</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>3.3829331408300573e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-9.7602915247296156e-05</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-6.4036910067599142e-05</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>0.00026256301163564519</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>0.00047485207338392605</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>3.0004915487036148e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0.0023286386745741123</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>0.00056217094916910298</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>0.0018833430366302164</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0041355496114984991</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.0062106763047060391</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.0059626766138754636</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>-0.00013245442831167178</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-0.00014920464817711854</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>0.00014520423976496213</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>0.00038564437905517579</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>0.0019161181337491065</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-8.1261694893552429e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>3.3819781328179709e-05</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="1">
         <v>-0.00039373274285970966</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="1">
         <v>7.6466964822948392e-05</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="1">
         <v>-5.9238629875559673e-05</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="1">
         <v>-9.3642418178923302e-06</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="1">
         <v>8.537344668939394e-05</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="1">
         <v>5.8836725553104621e-05</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="1">
         <v>0.0066233413512692381</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.017104914618258967</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-7.1180977395114204e-05</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-0.00040432064004843494</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>3.2749282788656398e-06</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-0.00010333604334471485</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-6.1566052407227524e-05</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.00074696228118203392</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>0.0010506496790185396</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-6.7235913653528392e-05</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0.0027463966344201075</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>0.00059230996288851421</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>0.0018907475316374905</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.0046667826728765092</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.0059626766138754636</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0078987179975718615</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>-9.253588677326965e-05</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-0.00012894189150488276</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>0.0001712955442313268</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>0.00042401656137758606</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>0.0024577636903764309</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>-3.9514469275853028e-06</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>1.4178790598661298e-05</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="1">
         <v>-0.00054126953012201273</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="1">
         <v>3.3770501426574982e-05</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="1">
         <v>-3.0677564530337195e-06</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="1">
         <v>7.7131913910058665e-07</v>
       </c>
-      <c r="AB15">
+      <c r="AB15" s="1">
         <v>8.3726434209647083e-05</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="1">
         <v>-2.3803820642253563e-05</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="1">
         <v>0.0044128420147115524</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.17549700445190405</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-0.00069320876602668659</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>0.00019055061330546658</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-1.2582308060409941e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0.00013005612827941045</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>9.940941965757167e-05</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-1.2647275010513822e-05</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>0.00013654720543211868</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-0.00052339291551085042</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-0.0013038711519999823</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>3.8074779593106787e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>3.547966556504236e-05</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-0.00021299043238716788</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-0.00013245442831167178</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>-9.253588677326965e-05</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0025522751356373517</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>-0.0001016365872977161</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>2.5241809667853662e-05</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>1.4992345109871366e-05</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>0.00015033850062681189</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-9.8462930250305504e-05</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>3.2137542325343712e-05</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="1">
         <v>6.4035954471459489e-05</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="1">
         <v>0.00017777550660127029</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="1">
         <v>-2.1115315429119934e-05</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="1">
         <v>-4.7320057902562357e-06</v>
       </c>
-      <c r="AB16">
+      <c r="AB16" s="1">
         <v>6.24215090562312e-05</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="1">
         <v>0.0001669162620475291</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="1">
         <v>-0.0061459267575353247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17">
+        <v>51</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.0077580810522399884</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-5.4814436400148041e-05</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>0.000672517382368093</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-6.8147082045526795e-06</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-5.4757104067465479e-05</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-0.00021078691488813847</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.00015298428650457993</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>0.00010931447430294491</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-0.00021549953571360463</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-0.0001410696180749074</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>0.00013691648243421492</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-4.6773360594432847e-05</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>0.00018959289887824</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-0.00014920464817711854</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-0.00012894189150488276</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>-0.0001016365872977161</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0032701967387638777</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-0.0021665852863260449</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-0.0019170873384277763</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-0.00058953180375786562</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>0.00053483957103960802</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>1.5974243406970123e-05</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="1">
         <v>-4.8125462266003895e-06</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="1">
         <v>-2.6549592973346484e-06</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="1">
         <v>0.00020172729574383672</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="1">
         <v>-2.0739563264337034e-05</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="1">
         <v>-2.3927696596144458e-05</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="1">
         <v>0.00082167802990473337</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="1">
         <v>-0.015927432420872644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.05260072189443897</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>0.00015128457546006134</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-0.0010598067095275304</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>9.3003271143169254e-06</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>9.6426344313751272e-05</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>0.00019748895890510723</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-9.7403745859787183e-05</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-6.2267503210837764e-05</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>0.00039465491332137635</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0.00026916697326754093</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-0.00025091683418665086</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>8.7986299791329315e-05</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-0.00012839296382699409</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>0.00014520423976496213</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>0.0001712955442313268</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>2.5241809667853662e-05</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-0.0021665852863260449</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.0048511900495357418</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.0016916718173627188</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>0.00032951691405389461</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-0.00027822733538281075</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-0.00010360731566091443</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="1">
         <v>-2.2706428446933906e-05</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="1">
         <v>9.8631103557064032e-05</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="1">
         <v>-0.00026020751482534288</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="1">
         <v>1.4134441504287188e-05</v>
       </c>
-      <c r="AB18">
+      <c r="AB18" s="1">
         <v>1.8128231858774435e-06</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="1">
         <v>-0.00082789223762412024</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="1">
         <v>0.029624168217203203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19">
+        <v>53</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.065074696222941583</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>8.0128530894044928e-05</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-0.00090260039600047193</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>7.8848899661843465e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>1.8043561853149648e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>9.9950698639376945e-05</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-0.00010779461062386766</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-1.0165985295352165e-05</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>0.00028729546376932494</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0.00029600308598087387</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-0.00010302291932961128</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>4.1368283494710089e-06</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-3.869527838100211e-05</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.00038564437905517579</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>0.00042401656137758606</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>1.4992345109871366e-05</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-0.0019170873384277763</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.0016916718173627188</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.005212198785663362</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>0.00029497759648064404</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-0.00030619479147920648</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-1.8540876819100882e-05</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="1">
         <v>0.00017538440008731462</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="1">
         <v>2.8338781613249098e-05</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="1">
         <v>-0.0001836073778115645</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="1">
         <v>-2.0655032169500311e-06</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="1">
         <v>4.9348179461554398e-05</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="1">
         <v>-0.00062430268426394778</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="1">
         <v>0.025417306745196346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.072827451375212807</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-6.9090894662101297e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-0.00011639641353401904</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>8.4808967769467556e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-0.0001023942288142757</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>-3.499973999983438e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.00015077354205447096</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.00018014772474622557</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.00011597883398200204</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0.00063937756240875867</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>0.00038562180615386198</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>2.4985499950073086e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>0.001298617951075188</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>0.0019161181337491065</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>0.0024577636903764309</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>0.00015033850062681189</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-0.00058953180375786562</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>0.00032951691405389461</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>0.00029497759648064404</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0022907937734431435</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.00078161945931567783</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-1.4530439383274134e-05</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="1">
         <v>-0.00024569226569922092</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="1">
         <v>-1.4629778449451979e-05</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="1">
         <v>0.00018931565691448905</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="1">
         <v>6.3350182252818789e-06</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="1">
         <v>0.00011890330911093244</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="1">
         <v>0.0002219311497160014</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="1">
         <v>0.00095015924346671034</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.053691414814330651</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>6.9571328676916672e-05</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-8.6944669574224448e-05</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>7.820747626408281e-07</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>1.970331722432779e-05</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>-5.9812013799018585e-06</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>2.9815800308848663e-05</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-4.4823300580725174e-05</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>0.00013233498735392216</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0.00032307995007107876</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-0.0003406080050491531</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-0.00014165866100096302</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-0.0002420732303093111</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-8.1261694893552429e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>-3.9514469275853028e-06</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-9.8462930250305504e-05</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>0.00053483957103960802</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-0.00027822733538281075</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-0.00030619479147920648</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.00078161945931567783</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.0030439503331933151</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>3.6519151509313065e-05</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>0.00017284437230233982</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="1">
         <v>6.6406233383591913e-06</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="1">
         <v>-0.00013216938208455758</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="1">
         <v>-1.1081493954941072e-05</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>7.6685850764083235e-06</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="1">
         <v>-6.9505999409703845e-05</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="1">
         <v>0.0025043459449772044</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1">
         <v>-0.13833687110001464</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-0.00025444586197862027</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>0.00030905641687004048</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-2.2023311793803913e-06</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>7.5743542655586776e-05</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>4.5740422671740333e-05</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>5.8429132797410742e-05</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>-5.3651335281894525e-05</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>-0.00034641005898824323</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>-0.0001884050393060146</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>0.00015993140580180653</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>3.8742391354317039e-05</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>-7.9854444786652684e-05</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>3.3819781328179709e-05</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>1.4178790598661298e-05</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>3.2137542325343712e-05</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>1.5974243406970123e-05</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-0.00010360731566091443</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-1.8540876819100882e-05</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-1.4530439383274134e-05</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>3.6519151509313065e-05</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.0025339827947987079</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>0.0013748807120391249</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="1">
         <v>0.0013552681439974773</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="1">
         <v>0.0013766657967369217</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="1">
         <v>-3.8652699203075804e-05</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="1">
         <v>0.00030636308540882599</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="1">
         <v>0.00011763115101354633</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="1">
         <v>-0.011023850538300298</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1">
         <v>0.017364743599326028</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>-7.3894526271214671e-05</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>0.00010353183581316219</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>-7.0474589703456588e-07</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>0.00010180699470342669</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>6.3612953440067132e-05</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>6.6867564640003802e-05</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>3.3329172839398764e-05</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>-0.00017064293500240703</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>-0.00023078656662817821</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>5.4313875407104289e-06</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>-0.00010385866329858044</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>-0.00039287227748727101</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>-0.00039373274285970966</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>-0.00054126953012201273</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>6.4035954471459489e-05</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>-4.8125462266003895e-06</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>-2.2706428446933906e-05</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>0.00017538440008731462</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>-0.00024569226569922092</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>0.00017284437230233982</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>0.0013748807120391249</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>0.0039014007956031703</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>0.0013779882903002579</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>0.0013896524081618443</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>-1.919244339780464e-05</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="1">
         <v>0.00010568722045325399</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="1">
         <v>-4.0335498411673762e-05</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="1">
         <v>-0.0041412627234079244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1">
         <v>-0.086167875102228453</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>-0.00024302535574699004</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>0.00025893234521229963</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>-1.7915606807792132e-06</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.00011350113251927876</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>4.1788134053605958e-05</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>0.00015588721984764682</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>8.004185158598672e-05</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>-0.00034724802772401718</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>-0.00024042802444643576</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>0.00010196590264069556</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>0.0001083999031252918</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>-0.00010359611343775492</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>7.6466964822948392e-05</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>3.3770501426574982e-05</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>0.00017777550660127029</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>-2.6549592973346484e-06</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>9.8631103557064032e-05</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>2.8338781613249098e-05</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>-1.4629778449451979e-05</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>6.6406233383591913e-06</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>0.0013552681439974773</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="1">
         <v>0.0013779882903002579</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="1">
         <v>0.0025568207474292188</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>0.0013612196558179265</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>-3.6584671033518228e-05</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>0.00024156000112688191</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="1">
         <v>0.00024374249725473752</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>-0.0096581082787350753</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1">
         <v>-0.07723983991887437</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>-0.00019984048134990217</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>0.00030593314854043298</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>-2.3790766378102053e-06</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>-1.2857853343623861e-05</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>7.9016643521681584e-07</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.00022144781212160854</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>2.498469268009414e-05</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>-0.00033982728298824006</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>-0.00019277017087081932</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>0.0002783875625854608</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>4.0935960010347774e-05</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>8.03628109896738e-05</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>-5.9238629875559673e-05</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>-3.0677564530337195e-06</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>-2.1115315429119934e-05</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>0.00020172729574383672</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>-0.00026020751482534288</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>-0.0001836073778115645</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>0.00018931565691448905</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="1">
         <v>-0.00013216938208455758</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>0.0013766657967369217</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="1">
         <v>0.0013896524081618443</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="1">
         <v>0.0013612196558179265</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="1">
         <v>0.00210645318534759</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="1">
         <v>-2.8197137570207472e-05</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="1">
         <v>0.00020194894303498151</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="1">
         <v>0.00048779968285382798</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="1">
         <v>-0.010735560886321166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1">
         <v>0.027735092164860836</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>2.1444089854963171e-05</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>-3.4503734812061423e-05</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>2.541625622577576e-07</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>-2.9307412868472926e-05</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>-2.8643883068854331e-05</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>5.9886420011594581e-06</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>3.2446506801741558e-05</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>6.119493947922747e-05</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>3.9449496683617311e-05</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>-2.7431189977497359e-05</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>-4.8204641563105729e-06</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>1.2494332885968593e-05</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-9.3642418178923302e-06</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>7.7131913910058665e-07</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>-4.7320057902562357e-06</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>-2.0739563264337034e-05</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>1.4134441504287188e-05</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>-2.0655032169500311e-06</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>6.3350182252818789e-06</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="1">
         <v>-1.1081493954941072e-05</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>-3.8652699203075804e-05</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>-1.919244339780464e-05</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="1">
         <v>-3.6584671033518228e-05</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="1">
         <v>-2.8197137570207472e-05</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="1">
         <v>3.0135931486633996e-05</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="1">
         <v>-0.00017217297048373727</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="1">
         <v>-0.00020422529426001446</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="1">
         <v>0.00064496676913944101</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27">
+        <v>56</v>
+      </c>
+      <c r="B27" s="1">
         <v>-0.54629872765746135</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>-0.00014009768424022573</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>0.0002356216591192159</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>-1.7413920244386096e-06</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>0.00014213532810521817</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>0.00012307294235631983</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>-5.7068512235385581e-05</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>-0.00010551115575253259</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>-0.00051433985085248823</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>-9.0537290877182059e-05</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>0.00021031350628897142</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>-6.3517107127158186e-06</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>-9.6553359474627672e-05</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>8.537344668939394e-05</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>8.3726434209647083e-05</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>6.24215090562312e-05</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>-2.3927696596144458e-05</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>1.8128231858774435e-06</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>4.9348179461554398e-05</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>0.00011890330911093244</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>7.6685850764083235e-06</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>0.00030636308540882599</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>0.00010568722045325399</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="1">
         <v>0.00024156000112688191</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="1">
         <v>0.00020194894303498151</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="1">
         <v>-0.00017217297048373727</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="1">
         <v>0.0038234130988946116</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="1">
         <v>0.0014943043050152599</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="1">
         <v>-0.0052863259887551677</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1">
         <v>-0.32113802779605832</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>-4.6906386195071786e-05</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>0.00080552715129966757</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>-6.8117122805056406e-06</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>-0.00027005352753556658</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>-0.00012268297274519238</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>0.00036774185934003049</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>3.7360027614460369e-05</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>-0.00064752532915221539</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>-0.0006786283533652673</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>0.00076822779751108171</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>0.00018316105101792235</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>0.00015215645559420133</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>5.8836725553104621e-05</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>-2.3803820642253563e-05</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>0.0001669162620475291</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>0.00082167802990473337</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>-0.00082789223762412024</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>-0.00062430268426394778</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>0.0002219311497160014</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>-6.9505999409703845e-05</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>0.00011763115101354633</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="1">
         <v>-4.0335498411673762e-05</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="1">
         <v>0.00024374249725473752</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="1">
         <v>0.00048779968285382798</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="1">
         <v>-0.00020422529426001446</v>
       </c>
-      <c r="AB28">
+      <c r="AB28" s="1">
         <v>0.0014943043050152599</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="1">
         <v>0.005672275142648211</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="1">
         <v>-0.021077767036781339</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29">
+        <v>48</v>
+      </c>
+      <c r="B29" s="1">
         <v>-12.118552936541803</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>0.013701474688218678</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>-0.14058478513640041</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>0.0011422518568260955</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>0.037121382055087887</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>0.037841740808914712</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>-0.0058017586293908673</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>-0.010963673573541305</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>0.0058628253836812191</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0.036400396432046414</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>-0.030164458624131398</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>-0.003490167919082768</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>0.0083695773642136553</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>0.0066233413512692381</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>0.0044128420147115524</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>-0.0061459267575353247</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>-0.015927432420872644</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>0.029624168217203203</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>0.025417306745196346</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>0.00095015924346671034</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>0.0025043459449772044</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>-0.011023850538300298</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="1">
         <v>-0.0041412627234079244</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="1">
         <v>-0.0096581082787350753</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="1">
         <v>-0.010735560886321166</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="1">
         <v>0.00064496676913944101</v>
       </c>
-      <c r="AB29">
+      <c r="AB29" s="1">
         <v>-0.0052863259887551677</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="1">
         <v>-0.021077767036781339</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="1">
         <v>4.2705953786597215</v>
       </c>
     </row>
